--- a/docs/The_Called_Client_Tracker_DEMO.xlsx
+++ b/docs/The_Called_Client_Tracker_DEMO.xlsx
@@ -2390,13 +2390,13 @@
         <v/>
       </c>
       <c r="C4" s="27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="27" t="n">
         <v>30</v>
       </c>
       <c r="E4" s="27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F4" s="27" t="n">
         <v>9</v>
@@ -2449,13 +2449,13 @@
         <v/>
       </c>
       <c r="C5" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="27" t="n">
         <v>31</v>
       </c>
       <c r="E5" s="27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F5" s="27" t="n">
         <v>9</v>
@@ -2504,13 +2504,13 @@
         <v/>
       </c>
       <c r="C6" s="27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="27" t="n">
         <v>28</v>
       </c>
       <c r="E6" s="27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F6" s="27" t="n">
         <v>9</v>
@@ -2559,13 +2559,13 @@
         <v/>
       </c>
       <c r="C7" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>34</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>10</v>
@@ -2614,13 +2614,13 @@
         <v/>
       </c>
       <c r="C8" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" s="27" t="n">
         <v>30</v>
       </c>
       <c r="E8" s="27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F8" s="27" t="n">
         <v>13</v>
@@ -2779,13 +2779,13 @@
         <v/>
       </c>
       <c r="C11" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" s="27" t="n">
         <v>35</v>
       </c>
       <c r="E11" s="27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F11" s="27" t="n">
         <v>13</v>
@@ -2834,13 +2834,13 @@
         <v/>
       </c>
       <c r="C12" s="27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="27" t="n">
         <v>35</v>
       </c>
       <c r="E12" s="27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>9</v>
@@ -2889,13 +2889,13 @@
         <v/>
       </c>
       <c r="C13" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" s="27" t="n">
         <v>33</v>
       </c>
       <c r="E13" s="27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F13" s="27" t="n">
         <v>12</v>
@@ -2944,13 +2944,13 @@
         <v/>
       </c>
       <c r="C14" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" s="27" t="n">
         <v>29</v>
       </c>
       <c r="E14" s="27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>11</v>
@@ -2999,13 +2999,13 @@
         <v/>
       </c>
       <c r="C15" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" s="27" t="n">
         <v>33</v>
       </c>
       <c r="E15" s="27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F15" s="27" t="n">
         <v>12</v>
@@ -3164,13 +3164,13 @@
         <v/>
       </c>
       <c r="C18" s="27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="27" t="n">
         <v>29</v>
       </c>
       <c r="E18" s="27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>10</v>
@@ -3219,13 +3219,13 @@
         <v/>
       </c>
       <c r="C19" s="27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" s="27" t="n">
         <v>32</v>
       </c>
       <c r="E19" s="27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F19" s="27" t="n">
         <v>9</v>
@@ -3333,13 +3333,13 @@
         <v/>
       </c>
       <c r="C21" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" s="27" t="n">
         <v>28</v>
       </c>
       <c r="E21" s="27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F21" s="27" t="n">
         <v>13</v>
@@ -3388,13 +3388,13 @@
         <v/>
       </c>
       <c r="C22" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" s="27" t="n">
         <v>34</v>
       </c>
       <c r="E22" s="27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>10</v>
@@ -3553,13 +3553,13 @@
         <v/>
       </c>
       <c r="C25" s="27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="27" t="n">
         <v>35</v>
       </c>
       <c r="E25" s="27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F25" s="27" t="n">
         <v>11</v>
@@ -3608,13 +3608,13 @@
         <v/>
       </c>
       <c r="C26" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" s="27" t="n">
         <v>30</v>
       </c>
       <c r="E26" s="27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F26" s="27" t="n">
         <v>9</v>
@@ -3663,13 +3663,13 @@
         <v/>
       </c>
       <c r="C27" s="27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" s="27" t="n">
         <v>36</v>
       </c>
       <c r="E27" s="27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F27" s="27" t="n">
         <v>9</v>
@@ -3718,13 +3718,13 @@
         <v/>
       </c>
       <c r="C28" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" s="27" t="n">
         <v>36</v>
       </c>
       <c r="E28" s="27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F28" s="27" t="n">
         <v>11</v>
@@ -3773,13 +3773,13 @@
         <v/>
       </c>
       <c r="C29" s="27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" s="27" t="n">
         <v>36</v>
       </c>
       <c r="E29" s="27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F29" s="27" t="n">
         <v>11</v>
@@ -3938,13 +3938,13 @@
         <v/>
       </c>
       <c r="C32" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D32" s="27" t="n">
         <v>29</v>
       </c>
       <c r="E32" s="27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F32" s="27" t="n">
         <v>9</v>
@@ -3993,13 +3993,13 @@
         <v/>
       </c>
       <c r="C33" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D33" s="27" t="n">
         <v>34</v>
       </c>
       <c r="E33" s="27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F33" s="27" t="n">
         <v>12</v>
@@ -4048,13 +4048,13 @@
         <v/>
       </c>
       <c r="C34" s="27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" s="27" t="n">
         <v>30</v>
       </c>
       <c r="E34" s="27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F34" s="27" t="n">
         <v>12</v>
@@ -4158,13 +4158,13 @@
         <v/>
       </c>
       <c r="C36" s="27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" s="27" t="n">
         <v>28</v>
       </c>
       <c r="E36" s="27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F36" s="27" t="n">
         <v>9</v>
@@ -4323,13 +4323,13 @@
         <v/>
       </c>
       <c r="C39" s="27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D39" s="27" t="n">
         <v>30</v>
       </c>
       <c r="E39" s="27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F39" s="27" t="n">
         <v>9</v>
@@ -4378,13 +4378,13 @@
         <v/>
       </c>
       <c r="C40" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D40" s="27" t="n">
         <v>28</v>
       </c>
       <c r="E40" s="27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F40" s="27" t="n">
         <v>13</v>
@@ -4433,13 +4433,13 @@
         <v/>
       </c>
       <c r="C41" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D41" s="27" t="n">
         <v>28</v>
       </c>
       <c r="E41" s="27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F41" s="27" t="n">
         <v>10</v>
@@ -4488,13 +4488,13 @@
         <v/>
       </c>
       <c r="C42" s="27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D42" s="27" t="n">
         <v>33</v>
       </c>
       <c r="E42" s="27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F42" s="27" t="n">
         <v>13</v>
@@ -4543,13 +4543,13 @@
         <v/>
       </c>
       <c r="C43" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D43" s="27" t="n">
         <v>36</v>
       </c>
       <c r="E43" s="27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F43" s="27" t="n">
         <v>13</v>
@@ -4708,13 +4708,13 @@
         <v/>
       </c>
       <c r="C46" s="27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D46" s="27" t="n">
         <v>31</v>
       </c>
       <c r="E46" s="27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F46" s="27" t="n">
         <v>9</v>
@@ -4763,13 +4763,13 @@
         <v/>
       </c>
       <c r="C47" s="27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D47" s="27" t="n">
         <v>34</v>
       </c>
       <c r="E47" s="27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F47" s="27" t="n">
         <v>12</v>
@@ -4818,13 +4818,13 @@
         <v/>
       </c>
       <c r="C48" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D48" s="27" t="n">
         <v>33</v>
       </c>
       <c r="E48" s="27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F48" s="27" t="n">
         <v>11</v>

--- a/docs/The_Called_Client_Tracker_DEMO.xlsx
+++ b/docs/The_Called_Client_Tracker_DEMO.xlsx
@@ -47,7 +47,7 @@
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="006B7280"/>
+      <color rgb="006E6A62"/>
       <sz val="10"/>
     </font>
     <font>
@@ -62,7 +62,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="006B4EFF"/>
+      <color rgb="003A3833"/>
       <sz val="10"/>
     </font>
     <font>
@@ -78,29 +78,29 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="006B7280"/>
+      <color rgb="006E6A62"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="006B7280"/>
+      <color rgb="006E6A62"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="006B4EFF"/>
+      <color rgb="003A3833"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="006B4EFF"/>
+      <color rgb="003A3833"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="006B7280"/>
+      <color rgb="006E6A62"/>
       <sz val="9"/>
     </font>
     <font>
@@ -109,7 +109,7 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="006B7280"/>
+      <color rgb="006E6A62"/>
       <sz val="8"/>
     </font>
     <font>
@@ -121,7 +121,7 @@
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="006B7280"/>
+      <color rgb="006E6A62"/>
       <sz val="8"/>
     </font>
     <font>
@@ -139,32 +139,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00111318"/>
+        <fgColor rgb="001B1916"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EFEAFF"/>
+        <fgColor rgb="00E1DFDB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6F4EA"/>
+        <fgColor rgb="00E7F0E5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF8DC"/>
+        <fgColor rgb="00FCF3E3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F1F3F5"/>
+        <fgColor rgb="00F2F1EF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="006B4EFF"/>
+        <fgColor rgb="003A3833"/>
       </patternFill>
     </fill>
   </fills>
@@ -178,30 +178,30 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D7DAE0"/>
+        <color rgb="00D6D3CC"/>
       </left>
       <right style="thin">
-        <color rgb="00D7DAE0"/>
+        <color rgb="00D6D3CC"/>
       </right>
       <top style="thin">
-        <color rgb="00D7DAE0"/>
+        <color rgb="00D6D3CC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D7DAE0"/>
+        <color rgb="00D6D3CC"/>
       </bottom>
     </border>
     <border>
       <left style="medium">
-        <color rgb="006B4EFF"/>
+        <color rgb="003A3833"/>
       </left>
       <right style="medium">
-        <color rgb="006B4EFF"/>
+        <color rgb="003A3833"/>
       </right>
       <top style="medium">
-        <color rgb="006B4EFF"/>
+        <color rgb="003A3833"/>
       </top>
       <bottom style="medium">
-        <color rgb="006B4EFF"/>
+        <color rgb="003A3833"/>
       </bottom>
     </border>
   </borders>
@@ -363,14 +363,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="00E6F4EA"/>
+          <bgColor rgb="00E7F0E5"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="00FCE8E6"/>
+          <bgColor rgb="00F7E4E0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -378,11 +378,11 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="00137333"/>
+        <color rgb="002F6B3A"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="00E6F4EA"/>
+          <bgColor rgb="00E7F0E5"/>
         </patternFill>
       </fill>
     </dxf>
@@ -390,22 +390,22 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="00C5221F"/>
+        <color rgb="00A83A2C"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="00FCE8E6"/>
+          <bgColor rgb="00F7E4E0"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
-        <color rgb="00C5221F"/>
+        <color rgb="00A83A2C"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="00FCE8E6"/>
+          <bgColor rgb="00F7E4E0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1589,7 +1589,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00111318"/>
+    <tabColor rgb="001B1916"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1984,7 +1984,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="006B4EFF"/>
+    <tabColor rgb="008E8A82"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2221,7 +2221,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="006B4EFF"/>
+    <tabColor rgb="008E8A82"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -14851,7 +14851,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00111318"/>
+    <tabColor rgb="001B1916"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -15847,7 +15847,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="006B4EFF"/>
+    <tabColor rgb="008E8A82"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -18171,7 +18171,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00111318"/>
+    <tabColor rgb="001B1916"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
